--- a/personal_forms/011_memory_book_submission_form--personal_forms.xlsx
+++ b/personal_forms/011_memory_book_submission_form--personal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>story_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>photo_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,63 +1165,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>photo_choices</t>
+          <t>photo_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>photo_choices</t>
+          <t>photo_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>photo_choices</t>
+          <t>photo_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
